--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/pre LAM_HRM-2031-0292/Panel 7/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/pre LAM_HRM-2031-0292/Panel 7/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.87573</v>
+        <v>16.88963</v>
       </c>
       <c r="D2" t="n">
-        <v>16.76378</v>
+        <v>16.49436</v>
       </c>
       <c r="E2" t="n">
-        <v>16.22834</v>
+        <v>16.60664</v>
       </c>
       <c r="F2" t="n">
-        <v>41.65403</v>
+        <v>42.28638</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0496</v>
+        <v>0.05068</v>
       </c>
       <c r="H2" t="n">
-        <v>1.80773</v>
+        <v>1.82786</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.66715</v>
+        <v>16.75681</v>
       </c>
       <c r="D3" t="n">
-        <v>16.31493</v>
+        <v>16.26346</v>
       </c>
       <c r="E3" t="n">
-        <v>16.60683</v>
+        <v>16.29893</v>
       </c>
       <c r="F3" t="n">
-        <v>41.47102</v>
+        <v>42.91505</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0508</v>
+        <v>0.05044</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84962</v>
+        <v>1.84806</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.8249</v>
+        <v>17.04017</v>
       </c>
       <c r="D4" t="n">
-        <v>16.49842</v>
+        <v>16.30812</v>
       </c>
       <c r="E4" t="n">
-        <v>16.41282</v>
+        <v>16.58588</v>
       </c>
       <c r="F4" t="n">
-        <v>42.91913</v>
+        <v>42.35273</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05065</v>
+        <v>0.05049</v>
       </c>
       <c r="H4" t="n">
-        <v>1.80949</v>
+        <v>1.85404</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.50637</v>
+        <v>16.61292</v>
       </c>
       <c r="D6" t="n">
-        <v>16.45901</v>
+        <v>16.15159</v>
       </c>
       <c r="E6" t="n">
-        <v>16.41853</v>
+        <v>16.30736</v>
       </c>
       <c r="F6" t="n">
-        <v>21.34769</v>
+        <v>21.77608</v>
       </c>
       <c r="G6" t="n">
-        <v>34.29578</v>
+        <v>33.69688</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.87829</v>
+        <v>16.98262</v>
       </c>
       <c r="D7" t="n">
-        <v>15.58559</v>
+        <v>16.01063</v>
       </c>
       <c r="E7" t="n">
-        <v>16.30708</v>
+        <v>16.66204</v>
       </c>
       <c r="F7" t="n">
-        <v>21.46647</v>
+        <v>21.72002</v>
       </c>
       <c r="G7" t="n">
-        <v>33.50389</v>
+        <v>33.99025</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.60794</v>
+        <v>16.81317</v>
       </c>
       <c r="D8" t="n">
-        <v>16.50606</v>
+        <v>16.41677</v>
       </c>
       <c r="E8" t="n">
-        <v>16.11142</v>
+        <v>16.71813</v>
       </c>
       <c r="F8" t="n">
-        <v>22.01077</v>
+        <v>21.52713</v>
       </c>
       <c r="G8" t="n">
-        <v>34.47494</v>
+        <v>34.82685</v>
       </c>
     </row>
   </sheetData>
